--- a/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
+++ b/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
@@ -5190,11 +5190,7 @@
         </is>
       </c>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
       <c r="F6" s="21"/>
       <c r="G6" s="24"/>
@@ -5212,29 +5208,25 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M6" s="24"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q6" s="24"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="S6" s="24"/>
@@ -5243,50 +5235,48 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
+          <t xml:space="preserve">㳞
 –汰</t>
         </is>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
+          <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ
+          <t xml:space="preserve">仲
 太</t>
         </is>
       </c>
@@ -5430,56 +5420,45 @@
       <c r="C10" s="24"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒣
-‹</t>
+          <t xml:space="preserve">㒣</t>
         </is>
       </c>
       <c r="O10" s="24"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="Q10" s="24"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S10" s="24"/>
@@ -5671,8 +5650,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴㄴ
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -5721,64 +5699,51 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄴ
-汰
-ﾉ</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ
-太
-ﾉ</t>
+          <t xml:space="preserve">仲
+太</t>
         </is>
       </c>
       <c r="O15" s="22"/>
       <c r="P15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q15" s="22"/>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-ﾉ
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -5795,7 +5760,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐ㄱ</t>
+          <t xml:space="preserve">㶐</t>
         </is>
       </c>
       <c r="G16" s="23"/>
@@ -5872,11 +5837,7 @@
         </is>
       </c>
       <c r="E18" s="24"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="24"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
@@ -5885,11 +5846,7 @@
         </is>
       </c>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -5898,11 +5855,7 @@
         </is>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="24"/>
       <c r="P18" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
+++ b/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
@@ -5235,48 +5235,49 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄴ
 汰</t>
         </is>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄴ
 –汰</t>
         </is>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄴ
 汰</t>
         </is>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄴ
 汰</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄴ
 汰</t>
         </is>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ㄴ
 太</t>
         </is>
       </c>
@@ -5650,7 +5651,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄴㄴ</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -5699,7 +5700,8 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -5711,39 +5713,45 @@
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㳞ㄴ
+汰
+ﾉ</t>
         </is>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-太</t>
+          <t xml:space="preserve">仲ㄴ
+太
+ﾉ</t>
         </is>
       </c>
       <c r="O15" s="22"/>
       <c r="P15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="Q15" s="22"/>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太
+ﾉ</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -5760,7 +5768,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐</t>
+          <t xml:space="preserve">㶐ㄱ</t>
         </is>
       </c>
       <c r="G16" s="23"/>

--- a/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
+++ b/sheets/조재수대금교본/검수/이누야사 (시대를 초월한 마음).xlsx
@@ -4955,30 +4955,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="101.66" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="101.66" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="101.66" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="101.66" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="101.66" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="101.66" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="101.66" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="101.66" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="101.66" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="101.66" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="S12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="101.66" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="101.66" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="101.66" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="101.66" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="101.66" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5834,7 +5834,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="101.66" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -5881,6 +5881,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
 </worksheet>
 </file>